--- a/output/Data and Chart Outputs/europe_tso_gas_demand_cee_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_cee_daily.xlsx
@@ -703,7 +703,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 01:43 UTC; 2102 days, 2021-01-01 to 2026-10-03</t>
+          <t>2026-10-04 01:44 UTC; 2102 days, 2021-01-01 to 2026-10-03</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_cee_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_cee_daily.xlsx
@@ -717,7 +717,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GWh per gas day. AT_total = AGGM 'determined consumption Austria flow' (end-customer consumption, allocated/metered; AGGM publishes it from Oct 2022 in this form); AT_slp = standard-load-profile customers, AT_industry_gt300 / AT_industry_lt300 = load-profile-metered customers above / below 300 MW capacity classes (AGGM naming), AT_power_east = gas-fired power plants in market area East only. CZ_total = NET4GAS system balance: CZ_border_entry (Brandov, Waidhaus, Lanzhot, Cesky Tesin) - CZ_border_exit + CZ_storage_withdrawal - CZ_storage_injection + CZ_production (virtual production point). NET4GAS publishes no domestic-exit series, so the balance is consumption plus own use, losses and line-pack change. LT_total = Amber Grid 'domestic consumption' = LT_distribution (gas transmitted to distribution systems) + LT_direct (to directly connected consumers); the latest day published is dropped as incomplete. Recent days are preliminary and restated.</t>
+          <t>GWh per gas day. AT_total = AGGM 'determined consumption Austria flow' (end-customer consumption, allocated/metered; AGGM publishes it from Oct 2022 in this form); AT_slp = standard-load-profile customers, AT_industry_gt300 / AT_industry_lt300 = load-profile-metered customers above / below 300 MW capacity classes (AGGM naming), AT_power_east = gas-fired power plants in market area East only. CZ_total = NET4GAS system balance: CZ_border_entry (Brandov, Waidhaus, Lanzhot, Cesky Tesin) - CZ_border_exit + CZ_storage_withdrawal - CZ_storage_injection + CZ_production (virtual production point). NET4GAS publishes no domestic-exit series, so the balance is consumption plus own use, losses and line-pack change. LT_total = Amber Grid 'domestic consumption' = LT_distribution (gas transmitted to distribution systems) + LT_direct (to directly connected consumers); the latest 3 days published are dropped as incomplete. Recent days are preliminary and restated.</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 01:52 UTC; 2102 days, 2021-01-01 to 2026-10-03</t>
+          <t>2026-10-04 01:54 UTC; 2102 days, 2021-01-01 to 2026-10-03</t>
         </is>
       </c>
     </row>
